--- a/KC_tableau_bts_e4.xlsx
+++ b/KC_tableau_bts_e4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtc\OneDrive\Desktop\SITE BTS SIO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtc\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E75DFF-5EB9-47E3-8A50-81B4B97B4900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594CD2F4-1FF1-4A49-BC4F-84319AD59525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,25 +16,62 @@
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$X$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$X$45</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="74">
+  <si>
+    <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
+  </si>
+  <si>
+    <t>SESSION 2024-2026</t>
+  </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
   </si>
   <si>
-    <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
+    <t>NOM et prénom : CHAVATTE Kurt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° candidat : </t>
+  </si>
+  <si>
+    <t>Centre de formation : AFPI Formation - Marcq-en-Baroeul</t>
   </si>
   <si>
     <t>Option :</t>
   </si>
   <si>
+    <t xml:space="preserve"> SISR</t>
+  </si>
+  <si>
     <t>▢ SLAM</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://kofejy.github.io/Kurt-Chavatte.SIO/</t>
+  </si>
+  <si>
+    <t>Signature du tuteur :</t>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -42,13 +79,93 @@
 (intitulé et liste des documents et productions associés)</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
-    <t xml:space="preserve"> SISR</t>
+    <t>A-Gérer le patrimoine informatique</t>
+  </si>
+  <si>
+    <t>B-Répondre aux incidents et aux demandes d’assistance et d’évolution</t>
+  </si>
+  <si>
+    <t>C-Développer la présence en ligne de l’organisation</t>
+  </si>
+  <si>
+    <t>D-Travailler en mode projet</t>
+  </si>
+  <si>
+    <t>E-Mettre à disposition des utilisateurs un service informatique</t>
+  </si>
+  <si>
+    <t>F-Organiser son développement professionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1▸Recenser et identifier les ressources numériques 
+ associés à un service
+</t>
+  </si>
+  <si>
+    <t>2▸Exploiter des référentiels, normes et standards adoptés par le prestataire informatique</t>
+  </si>
+  <si>
+    <t>3▸Mettre en place et vérifier les niveaux d’habilitation</t>
+  </si>
+  <si>
+    <t>4▸Vérifier les conditions de la continuité d’un service informatique</t>
+  </si>
+  <si>
+    <t>5▸Gérer des sauvegardes</t>
+  </si>
+  <si>
+    <t>6▸Vérifier le respect des règles d’utilisation des ressources numériques</t>
+  </si>
+  <si>
+    <t>1▸Collecter, suivre et orienter des demandes</t>
+  </si>
+  <si>
+    <t>2▸Traiter des demandes concernant les services réseau et système, applicatifs</t>
+  </si>
+  <si>
+    <t>3▸Traiter des demandes concernant les applications</t>
+  </si>
+  <si>
+    <t>1▸Participer à la valorisation de l’image de l’organisation sur les médias numériques en tenant compte du cadre juridique et des enjeux économiques</t>
+  </si>
+  <si>
+    <t>2▸Référencer les services en ligne de l’organisation et mesurer leur visibilité.</t>
+  </si>
+  <si>
+    <t>3▸Participer à l’évolution d’un site Web exploitant les données de l’organisation.</t>
+  </si>
+  <si>
+    <t>1▸Analyser les objectifs et les modalités d’organisation d’un projet</t>
+  </si>
+  <si>
+    <t>2▸Planifier les activités</t>
+  </si>
+  <si>
+    <t>3▸Évaluer les indicateurs de suivi d’un projet et analyser les écarts</t>
+  </si>
+  <si>
+    <t>1▸Réaliser les tests d’intégration et d’acceptation d’un service</t>
+  </si>
+  <si>
+    <t>2▸Déployer un service</t>
+  </si>
+  <si>
+    <t>3▸Accompagner les utilisateurs dans la mise en place d’un service</t>
+  </si>
+  <si>
+    <t>1▸Mettre en place son environnement d’apprentissage personnel</t>
+  </si>
+  <si>
+    <t>2▸Mettre en œuvre des outils et stratégies de veille informationnelle</t>
+  </si>
+  <si>
+    <t>3▸Gérer son identité professionnelle</t>
+  </si>
+  <si>
+    <t>4▸Développer son projet professionnel</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -56,86 +173,6 @@
   </si>
   <si>
     <t xml:space="preserve">
-</t>
-  </si>
-  <si>
-    <t>Centre de formation : AFPI</t>
-  </si>
-  <si>
-    <t>SESSION 2024-2026</t>
-  </si>
-  <si>
-    <t>A-Gérer le patrimoine informatique</t>
-  </si>
-  <si>
-    <t>B-Répondre aux incidents et aux demandes d’assistance et d’évolution</t>
-  </si>
-  <si>
-    <t>C-Développer la présence en ligne de l’organisation</t>
-  </si>
-  <si>
-    <t>D-Travailler en mode projet</t>
-  </si>
-  <si>
-    <t>E-Mettre à disposition des utilisateurs un service informatique</t>
-  </si>
-  <si>
-    <t>F-Organiser son développement professionnel</t>
-  </si>
-  <si>
-    <t>2▸Exploiter des référentiels, normes et standards adoptés par le prestataire informatique</t>
-  </si>
-  <si>
-    <t>3▸Mettre en place et vérifier les niveaux d’habilitation</t>
-  </si>
-  <si>
-    <t>4▸Vérifier les conditions de la continuité d’un service informatique</t>
-  </si>
-  <si>
-    <t>5▸Gérer des sauvegardes</t>
-  </si>
-  <si>
-    <t>6▸Vérifier le respect des règles d’utilisation des ressources numériques</t>
-  </si>
-  <si>
-    <t>1▸Collecter, suivre et orienter des demandes</t>
-  </si>
-  <si>
-    <t>2▸Traiter des demandes concernant les services réseau et système, applicatifs</t>
-  </si>
-  <si>
-    <t>3▸Traiter des demandes concernant les applications</t>
-  </si>
-  <si>
-    <t>1▸Participer à la valorisation de l’image de l’organisation sur les médias numériques en tenant compte du cadre juridique et des enjeux économiques</t>
-  </si>
-  <si>
-    <t>2▸Référencer les services en ligne de l’organisation et mesurer leur visibilité.</t>
-  </si>
-  <si>
-    <t>1▸Analyser les objectifs et les modalités d’organisation d’un projet</t>
-  </si>
-  <si>
-    <t>3▸Évaluer les indicateurs de suivi d’un projet et analyser les écarts</t>
-  </si>
-  <si>
-    <t>1▸Réaliser les tests d’intégration et d’acceptation d’un service</t>
-  </si>
-  <si>
-    <t>2▸Déployer un service</t>
-  </si>
-  <si>
-    <t>1▸Mettre en place son environnement d’apprentissage personnel</t>
-  </si>
-  <si>
-    <t>2▸Mettre en œuvre des outils et stratégies de veille informationnelle</t>
-  </si>
-  <si>
-    <t>3▸Gérer son identité professionnelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1▸Recenser et identifier les ressources numériques 
- associés à un service
 </t>
   </si>
   <si>
@@ -162,106 +199,94 @@
     </r>
   </si>
   <si>
-    <t>2▸Planifier les activités</t>
-  </si>
-  <si>
-    <t>3▸Participer à l’évolution d’un site Web exploitant les données de l’organisation.</t>
-  </si>
-  <si>
-    <t>3▸Accompagner les utilisateurs dans la mise en place d’un service</t>
-  </si>
-  <si>
-    <t>4▸Développer son projet professionnel</t>
-  </si>
-  <si>
-    <t>NOM et prénom : CHAVATTE Kurt</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio : https://kofejy.github.io/Kurt-Chavatte.SIO/</t>
+    <t>Élaboration de la nomenclature des équipements et du plan d'adressage IP (tableau des IPs, vSwitch ESXi).</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Mise en œuvre des standards réseau : segmentation par VLAN, attribution dynamique des adresses (DHCP), résolution de noms (DNS) et chiffrement des communications (IPsec).</t>
+  </si>
+  <si>
+    <t>Gestion des habilitations Active Directory : création des OUs, des groupes (GG_Employés, GDL_Partage…) et application des GPO.</t>
+  </si>
+  <si>
+    <t>Mise en place de la haute disponibilité web via HAProxy en répartition de charge round-robin entre WEB-01 et WEB-02.</t>
+  </si>
+  <si>
+    <t>Mise en place d'une authentification 802.1X via RADIUS/NPS pour sécuriser l'accès au Wi-Fi saisonnier.</t>
+  </si>
+  <si>
+    <t>Configuration du switch, du pare-feu Stormshield, de l'hyperviseur ESXi et des accès SSH sur les serveurs Debian.</t>
+  </si>
+  <si>
+    <t>Déploiement de la messagerie Zimbra et de la stack web Apache/PHP/MariaDB.</t>
+  </si>
+  <si>
+    <t>Analyse de l'architecture globale de l'infrastructure et définition des objectifs du projet.</t>
+  </si>
+  <si>
+    <t>Planification du déploiement par étapes : matériel, Active Directory, serveurs Linux puis DMZ.</t>
+  </si>
+  <si>
+    <t>Tests de connectivité SSH et vérification de l'état des services via systemctl status et zmcontrol status.</t>
+  </si>
+  <si>
+    <t>Déploiement complet de l'infrastructure : switch, pare-feu, ESXi, Active Directory et serveurs Linux.</t>
+  </si>
+  <si>
+    <t>Déploiement d'un poste client Windows 10, intégration au domaine, validation des GPO et rédaction de la documentation.</t>
+  </si>
+  <si>
+    <t>Rédaction et production de la documentation technique complète de l'infrastructure.</t>
+  </si>
+  <si>
+    <t>Création d'un portefolio sous format site WEB</t>
+  </si>
+  <si>
+    <t>Réalisations en milieu professionnel au cours de la première année</t>
   </si>
   <si>
     <t>Mise en place borne Wi-Fi</t>
   </si>
   <si>
-    <t>00/04/2025</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>Réalisations en milieu professionnel au cours de la deuxième année</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Masterisation" des postes (Reformatage avec ISO windows spécifique aux besoins de l'entreprise), Mise à jour de l'inventaire PC sur GLPI </t>
+  </si>
+  <si>
+    <t>(Différents tickets)</t>
   </si>
   <si>
     <t>Configuration d'imprimantes</t>
   </si>
   <si>
-    <t>(Différents tickets)</t>
-  </si>
-  <si>
     <t>Gestion de crise migration microsoft (outlook, teams, one drive)</t>
   </si>
   <si>
-    <t>Réalisations en milieu professionnel au cours de la première année</t>
-  </si>
-  <si>
-    <t>Réalisations en milieu professionnel au cours de la deuxième année</t>
-  </si>
-  <si>
-    <t>Élaboration de la nomenclature des équipements et du plan d'adressage IP (tableau des IPs, vSwitch ESXi).</t>
-  </si>
-  <si>
-    <t>Mise en œuvre des standards réseau : segmentation par VLAN, attribution dynamique des adresses (DHCP), résolution de noms (DNS) et chiffrement des communications (IPsec).</t>
-  </si>
-  <si>
-    <t>Gestion des habilitations Active Directory : création des OUs, des groupes (GG_Employés, GDL_Partage…) et application des GPO.</t>
-  </si>
-  <si>
-    <t>Mise en place de la haute disponibilité web via HAProxy en répartition de charge round-robin entre WEB-01 et WEB-02.</t>
-  </si>
-  <si>
-    <t>Mise en place d'une authentification 802.1X via RADIUS/NPS pour sécuriser l'accès au Wi-Fi saisonnier.</t>
-  </si>
-  <si>
-    <t>Configuration du switch, du pare-feu Stormshield, de l'hyperviseur ESXi et des accès SSH sur les serveurs Debian.</t>
-  </si>
-  <si>
-    <t>Déploiement de la messagerie Zimbra et de la stack web Apache/PHP/MariaDB.</t>
-  </si>
-  <si>
-    <t>Analyse de l'architecture globale de l'infrastructure et définition des objectifs du projet.</t>
-  </si>
-  <si>
-    <t>Planification du déploiement par étapes : matériel, Active Directory, serveurs Linux puis DMZ.</t>
-  </si>
-  <si>
-    <t>Déploiement complet de l'infrastructure : switch, pare-feu, ESXi, Active Directory et serveurs Linux.</t>
-  </si>
-  <si>
-    <t>Tests de connectivité SSH et vérification de l'état des services via systemctl status et zmcontrol status.</t>
-  </si>
-  <si>
-    <t>Déploiement d'un poste client Windows 10, intégration au domaine, validation des GPO et rédaction de la documentation.</t>
-  </si>
-  <si>
-    <t>Rédaction et production de la documentation technique complète de l'infrastructure.</t>
-  </si>
-  <si>
     <t>27/11/2025 au 15/12/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">"Masterisation" des postes (Reformatage avec ISO windows spécifique aux besoins de l'entreprise), Mise à jour de l'inventaire PC sur GLPI </t>
-  </si>
-  <si>
-    <t>23/05 au 25/05/2026</t>
-  </si>
-  <si>
     <t>Changements mots de passe suite à demande utilisateur</t>
   </si>
   <si>
+    <t>Attribution des différentes Équipes et canaux Teams aux utilisateurs concernés</t>
+  </si>
+  <si>
+    <t>(Tous les mois)</t>
+  </si>
+  <si>
     <t>Panne réseau  (prise d'appels, explication de la situation aux utilisateurs)</t>
   </si>
   <si>
-    <t>Attribution des différentes Équpes et canaux Teams aux utilisateurs concernés</t>
-  </si>
-  <si>
-    <t>(Tout les mois)</t>
+    <t>23/03 au 25/03/2026</t>
+  </si>
+  <si>
+    <t>Recensement des solutions réseau par site</t>
+  </si>
+  <si>
+    <t>01/02 au 24/04/2026</t>
   </si>
 </sst>
 </file>
@@ -378,7 +403,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -639,26 +664,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -713,17 +718,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -796,12 +790,171 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalDown="1">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -818,18 +971,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
@@ -887,6 +1028,124 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -905,13 +1164,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -929,186 +1209,56 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1467,7 +1617,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BG91"/>
+  <dimension ref="A1:BG93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="135.5546875" style="1" customWidth="1"/>
@@ -1478,346 +1628,305 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="31"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="67"/>
     </row>
     <row r="2" spans="1:59" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="42"/>
+      <c r="A2" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="84"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="84"/>
+      <c r="W2" s="84"/>
+      <c r="X2" s="85"/>
     </row>
     <row r="3" spans="1:59" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="36"/>
+      <c r="A3" s="69" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="70"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="74"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
     <row r="4" spans="1:59" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
+    </row>
+    <row r="5" spans="1:59" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="91" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="93"/>
+      <c r="P5" s="93"/>
+      <c r="Q5" s="93"/>
+      <c r="R5" s="93"/>
+      <c r="S5" s="93"/>
+      <c r="T5" s="93"/>
+      <c r="U5" s="93"/>
+      <c r="V5" s="93"/>
+      <c r="W5" s="93"/>
+      <c r="X5" s="94"/>
+    </row>
+    <row r="6" spans="1:59" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="8"/>
-    </row>
-    <row r="5" spans="1:59" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="53"/>
-      <c r="U5" s="53"/>
-      <c r="V5" s="53"/>
-      <c r="W5" s="53"/>
-      <c r="X5" s="54"/>
-    </row>
-    <row r="6" spans="1:59" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="57" t="s">
-        <v>13</v>
-      </c>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
       <c r="J6" s="58"/>
       <c r="K6" s="58"/>
-      <c r="L6" s="55" t="s">
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="58"/>
+      <c r="U6" s="58"/>
+      <c r="V6" s="58"/>
+      <c r="W6" s="58"/>
+      <c r="X6" s="59"/>
+    </row>
+    <row r="7" spans="1:59" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="59" t="s">
+      <c r="J7" s="98"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="59" t="s">
+      <c r="M7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="S6" s="60"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="59" t="s">
+      <c r="P7" s="100"/>
+      <c r="Q7" s="101"/>
+      <c r="R7" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="V6" s="60"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="62"/>
-      <c r="AK6" s="11"/>
-      <c r="AL6" s="11"/>
-      <c r="AM6" s="11"/>
-      <c r="AN6" s="11"/>
-      <c r="AO6" s="11"/>
-    </row>
-    <row r="7" spans="1:59" s="2" customFormat="1" ht="205.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="25" t="s">
+      <c r="S7" s="100"/>
+      <c r="T7" s="101"/>
+      <c r="U7" s="99" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="100"/>
+      <c r="W7" s="100"/>
+      <c r="X7" s="102"/>
+      <c r="AK7" s="7"/>
+      <c r="AL7" s="7"/>
+      <c r="AM7" s="7"/>
+      <c r="AN7" s="7"/>
+      <c r="AO7" s="7"/>
+    </row>
+    <row r="8" spans="1:59" s="2" customFormat="1" ht="204.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="81"/>
+      <c r="B8" s="90"/>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="S8" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="27" t="s">
+      <c r="T8" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="V8" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q7" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="R7" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="S7" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="27" t="s">
+      <c r="W8" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="U7" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="V7" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="W7" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="X7" s="28" t="s">
+      <c r="X8" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7"/>
-      <c r="AC7"/>
-      <c r="AD7"/>
-      <c r="AE7"/>
-      <c r="AF7"/>
-      <c r="AG7"/>
-      <c r="AH7"/>
-      <c r="AI7"/>
-      <c r="AJ7"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO7" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AP7"/>
-      <c r="AQ7"/>
-      <c r="AR7"/>
-      <c r="AS7"/>
-      <c r="AT7"/>
-      <c r="AU7"/>
-      <c r="AV7"/>
-      <c r="AW7"/>
-      <c r="AX7"/>
-      <c r="AY7"/>
-      <c r="AZ7"/>
-      <c r="BA7"/>
-      <c r="BB7"/>
-      <c r="BC7"/>
-      <c r="BD7"/>
-      <c r="BE7"/>
-      <c r="BF7"/>
-      <c r="BG7"/>
-    </row>
-    <row r="8" spans="1:59" s="2" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="44"/>
-      <c r="W8" s="44"/>
-      <c r="X8" s="45"/>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8"/>
@@ -1827,11 +1936,17 @@
       <c r="AH8"/>
       <c r="AI8"/>
       <c r="AJ8"/>
-      <c r="AK8"/>
-      <c r="AL8"/>
-      <c r="AM8"/>
-      <c r="AN8"/>
-      <c r="AO8"/>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO8" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="AP8"/>
       <c r="AQ8"/>
       <c r="AR8"/>
@@ -1851,37 +1966,33 @@
       <c r="BF8"/>
       <c r="BG8"/>
     </row>
-    <row r="9" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="103" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="23">
-        <v>46113</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="91"/>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="93"/>
-      <c r="R9" s="91"/>
-      <c r="S9" s="92"/>
-      <c r="T9" s="93"/>
-      <c r="U9" s="94"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="15"/>
+    <row r="9" spans="1:59" s="2" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="86" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
+      <c r="M9" s="87"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="87"/>
+      <c r="P9" s="87"/>
+      <c r="Q9" s="87"/>
+      <c r="R9" s="87"/>
+      <c r="S9" s="87"/>
+      <c r="T9" s="87"/>
+      <c r="U9" s="87"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="87"/>
+      <c r="X9" s="88"/>
       <c r="Y9"/>
       <c r="Z9"/>
       <c r="AA9"/>
@@ -1918,37 +2029,39 @@
       <c r="BF9"/>
       <c r="BG9"/>
     </row>
-    <row r="10" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="23">
-        <v>46054</v>
-      </c>
-      <c r="C10" s="95"/>
-      <c r="D10" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="97"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="95"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="95"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="97"/>
-      <c r="R10" s="95"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="97"/>
-      <c r="U10" s="98"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="16"/>
+    <row r="10" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="19">
+        <v>46113</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="52"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="11"/>
       <c r="Y10"/>
       <c r="Z10"/>
       <c r="AA10"/>
@@ -1985,37 +2098,39 @@
       <c r="BF10"/>
       <c r="BG10"/>
     </row>
-    <row r="11" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="23">
-        <v>46082</v>
-      </c>
-      <c r="C11" s="95"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="95"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="97"/>
-      <c r="O11" s="95"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="97"/>
-      <c r="R11" s="95"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="97"/>
-      <c r="U11" s="98"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="16"/>
+    <row r="11" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="19">
+        <v>46054</v>
+      </c>
+      <c r="C11" s="53"/>
+      <c r="D11" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="53"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="T11" s="12"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="12"/>
       <c r="Y11"/>
       <c r="Z11"/>
       <c r="AA11"/>
@@ -2052,37 +2167,39 @@
       <c r="BF11"/>
       <c r="BG11"/>
     </row>
-    <row r="12" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="23">
-        <v>46054</v>
-      </c>
-      <c r="C12" s="95"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="96"/>
-      <c r="H12" s="97"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="95"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="97"/>
-      <c r="O12" s="95"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="97"/>
-      <c r="R12" s="95"/>
-      <c r="S12" s="96"/>
-      <c r="T12" s="97"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="16"/>
+    <row r="12" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="19">
+        <v>46082</v>
+      </c>
+      <c r="C12" s="53"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="U12" s="54"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="12"/>
       <c r="Y12"/>
       <c r="Z12"/>
       <c r="AA12"/>
@@ -2119,37 +2236,39 @@
       <c r="BF12"/>
       <c r="BG12"/>
     </row>
-    <row r="13" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="23">
+    <row r="13" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="19">
         <v>46054</v>
       </c>
-      <c r="C13" s="95"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="95"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="95"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="97"/>
-      <c r="O13" s="95"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="97"/>
-      <c r="R13" s="95"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="97"/>
-      <c r="U13" s="98"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="13"/>
-      <c r="X13" s="16"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="9"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="U13" s="54"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="12"/>
       <c r="Y13"/>
       <c r="Z13"/>
       <c r="AA13"/>
@@ -2187,36 +2306,38 @@
       <c r="BG13"/>
     </row>
     <row r="14" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="23">
-        <v>46023</v>
-      </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="K14" s="97"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="97"/>
-      <c r="O14" s="95"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="97"/>
-      <c r="R14" s="95"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="97"/>
-      <c r="U14" s="98"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="16"/>
+      <c r="A14" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="19">
+        <v>46054</v>
+      </c>
+      <c r="C14" s="53"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="53"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="T14" s="12"/>
+      <c r="U14" s="54"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="12"/>
       <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
@@ -2254,36 +2375,38 @@
       <c r="BG14"/>
     </row>
     <row r="15" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="23">
-        <v>46082</v>
-      </c>
-      <c r="C15" s="95"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="97"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="L15" s="95"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="97"/>
-      <c r="O15" s="95"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="97"/>
-      <c r="R15" s="95"/>
-      <c r="S15" s="96"/>
-      <c r="T15" s="97"/>
-      <c r="U15" s="98"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="16"/>
+      <c r="A15" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="19">
+        <v>46023</v>
+      </c>
+      <c r="C15" s="53"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="T15" s="12"/>
+      <c r="U15" s="54"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="12"/>
       <c r="Y15"/>
       <c r="Z15"/>
       <c r="AA15"/>
@@ -2320,37 +2443,37 @@
       <c r="BF15"/>
       <c r="BG15"/>
     </row>
-    <row r="16" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="23">
-        <v>46023</v>
-      </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="97"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="96"/>
-      <c r="N16" s="97"/>
-      <c r="O16" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="97"/>
-      <c r="R16" s="95"/>
-      <c r="S16" s="96"/>
-      <c r="T16" s="97"/>
-      <c r="U16" s="98"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="13"/>
-      <c r="X16" s="16"/>
+    <row r="16" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="19">
+        <v>46082</v>
+      </c>
+      <c r="C16" s="53"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="T16" s="12"/>
+      <c r="U16" s="54"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="12"/>
       <c r="Y16"/>
       <c r="Z16"/>
       <c r="AA16"/>
@@ -2387,37 +2510,37 @@
       <c r="BF16"/>
       <c r="BG16"/>
     </row>
-    <row r="17" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="23">
+    <row r="17" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="19">
         <v>46023</v>
       </c>
-      <c r="C17" s="95"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="97"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="97"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="97"/>
-      <c r="O17" s="95"/>
-      <c r="P17" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q17" s="97"/>
-      <c r="R17" s="95"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="97"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="16"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="12"/>
       <c r="Y17"/>
       <c r="Z17"/>
       <c r="AA17"/>
@@ -2454,37 +2577,37 @@
       <c r="BF17"/>
       <c r="BG17"/>
     </row>
-    <row r="18" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="23">
-        <v>46082</v>
-      </c>
-      <c r="C18" s="95"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="95"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="S18" s="96"/>
-      <c r="T18" s="97"/>
-      <c r="U18" s="98"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="16"/>
+    <row r="18" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="19">
+        <v>46023</v>
+      </c>
+      <c r="C18" s="53"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="54"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="12"/>
       <c r="Y18"/>
       <c r="Z18"/>
       <c r="AA18"/>
@@ -2521,37 +2644,39 @@
       <c r="BF18"/>
       <c r="BG18"/>
     </row>
-    <row r="19" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="23">
+    <row r="19" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="19">
         <v>46082</v>
       </c>
-      <c r="C19" s="95"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="95"/>
-      <c r="P19" s="96"/>
-      <c r="Q19" s="97"/>
-      <c r="R19" s="95"/>
-      <c r="S19" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="T19" s="97"/>
-      <c r="U19" s="98"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="16"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="S19" s="9"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="54"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="12"/>
       <c r="Y19"/>
       <c r="Z19"/>
       <c r="AA19"/>
@@ -2588,37 +2713,45 @@
       <c r="BF19"/>
       <c r="BG19"/>
     </row>
-    <row r="20" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="23">
-        <v>46054</v>
-      </c>
-      <c r="C20" s="95"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="97"/>
-      <c r="L20" s="95"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="95"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="97"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="U20" s="98"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="16"/>
+    <row r="20" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="19">
+        <v>46082</v>
+      </c>
+      <c r="C20" s="53"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="M20" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="N20" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="O20" s="53"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="T20" s="12"/>
+      <c r="U20" s="54"/>
+      <c r="V20" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="W20" s="9"/>
+      <c r="X20" s="12"/>
       <c r="Y20"/>
       <c r="Z20"/>
       <c r="AA20"/>
@@ -2656,36 +2789,36 @@
       <c r="BG20"/>
     </row>
     <row r="21" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="24">
-        <v>46113</v>
-      </c>
-      <c r="C21" s="99"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="100"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="100"/>
-      <c r="N21" s="101"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="100"/>
-      <c r="Q21" s="101"/>
-      <c r="R21" s="102"/>
-      <c r="S21" s="100"/>
-      <c r="T21" s="101"/>
-      <c r="U21" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="18"/>
+      <c r="A21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="19">
+        <v>46054</v>
+      </c>
+      <c r="C21" s="53"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="U21" s="54"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="12"/>
       <c r="Y21"/>
       <c r="Z21"/>
       <c r="AA21"/>
@@ -2722,33 +2855,37 @@
       <c r="BF21"/>
       <c r="BG21"/>
     </row>
-    <row r="22" spans="1:59" s="2" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="49"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="49"/>
-      <c r="R22" s="49"/>
-      <c r="S22" s="49"/>
-      <c r="T22" s="49"/>
-      <c r="U22" s="49"/>
-      <c r="V22" s="49"/>
-      <c r="W22" s="49"/>
-      <c r="X22" s="50"/>
+    <row r="22" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="20">
+        <v>46113</v>
+      </c>
+      <c r="C22" s="55"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="14"/>
       <c r="Y22"/>
       <c r="Z22"/>
       <c r="AA22"/>
@@ -2785,41 +2922,49 @@
       <c r="BF22"/>
       <c r="BG22"/>
     </row>
-    <row r="23" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="65"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="67"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="67"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="68"/>
-      <c r="V23" s="67"/>
-      <c r="W23" s="67"/>
-      <c r="X23" s="65"/>
+    <row r="23" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="20">
+        <v>46113</v>
+      </c>
+      <c r="C23" s="55"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="P23" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="R23" s="56"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="V23" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="W23" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="X23" s="26" t="s">
+        <v>45</v>
+      </c>
       <c r="Y23"/>
       <c r="Z23"/>
       <c r="AA23"/>
@@ -2857,32 +3002,32 @@
       <c r="BG23"/>
     </row>
     <row r="24" spans="1:59" s="2" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="47"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="49"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="49"/>
-      <c r="R24" s="49"/>
-      <c r="S24" s="49"/>
-      <c r="T24" s="49"/>
-      <c r="U24" s="49"/>
-      <c r="V24" s="49"/>
-      <c r="W24" s="49"/>
-      <c r="X24" s="50"/>
+      <c r="A24" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="76"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="78"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="78"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="78"/>
+      <c r="N24" s="78"/>
+      <c r="O24" s="78"/>
+      <c r="P24" s="78"/>
+      <c r="Q24" s="78"/>
+      <c r="R24" s="78"/>
+      <c r="S24" s="78"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="78"/>
+      <c r="V24" s="78"/>
+      <c r="W24" s="78"/>
+      <c r="X24" s="79"/>
       <c r="Y24"/>
       <c r="Z24"/>
       <c r="AA24"/>
@@ -2920,50 +3065,38 @@
       <c r="BG24"/>
     </row>
     <row r="25" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="I25" s="72"/>
-      <c r="J25" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="K25" s="71"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="73"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="S25" s="73"/>
-      <c r="T25" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="U25" s="74"/>
-      <c r="V25" s="73"/>
-      <c r="W25" s="73"/>
-      <c r="X25" s="71"/>
+      <c r="A25" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="19">
+        <v>45748</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="27"/>
       <c r="Y25"/>
       <c r="Z25"/>
       <c r="AA25"/>
@@ -3000,41 +3133,33 @@
       <c r="BF25"/>
       <c r="BG25"/>
     </row>
-    <row r="26" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="J26" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="K26" s="71"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="73"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="73"/>
-      <c r="Q26" s="71"/>
-      <c r="R26" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="S26" s="73"/>
-      <c r="T26" s="71"/>
-      <c r="U26" s="74"/>
-      <c r="V26" s="73"/>
-      <c r="W26" s="73"/>
-      <c r="X26" s="71"/>
+    <row r="26" spans="1:59" s="2" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="78"/>
+      <c r="M26" s="78"/>
+      <c r="N26" s="78"/>
+      <c r="O26" s="78"/>
+      <c r="P26" s="78"/>
+      <c r="Q26" s="78"/>
+      <c r="R26" s="78"/>
+      <c r="S26" s="78"/>
+      <c r="T26" s="78"/>
+      <c r="U26" s="78"/>
+      <c r="V26" s="78"/>
+      <c r="W26" s="78"/>
+      <c r="X26" s="79"/>
       <c r="Y26"/>
       <c r="Z26"/>
       <c r="AA26"/>
@@ -3072,40 +3197,52 @@
       <c r="BG26"/>
     </row>
     <row r="27" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="J27" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="K27" s="69"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="73"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="74"/>
-      <c r="S27" s="73"/>
-      <c r="T27" s="71"/>
-      <c r="U27" s="74"/>
-      <c r="V27" s="73"/>
-      <c r="W27" s="73"/>
-      <c r="X27" s="71"/>
+      <c r="A27" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K27" s="33"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="S27" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="T27" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="U27" s="35"/>
+      <c r="V27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="X27" s="33"/>
       <c r="Y27"/>
       <c r="Z27"/>
       <c r="AA27"/>
@@ -3142,43 +3279,43 @@
       <c r="BF27"/>
       <c r="BG27"/>
     </row>
-    <row r="28" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="76"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="J28" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="K28" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="L28" s="74"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="71"/>
-      <c r="R28" s="74"/>
-      <c r="S28" s="73"/>
-      <c r="T28" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="U28" s="74"/>
-      <c r="V28" s="73"/>
-      <c r="W28" s="73"/>
-      <c r="X28" s="71"/>
+    <row r="28" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="31"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28" s="33"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="T28" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="U28" s="35"/>
+      <c r="V28" s="34"/>
+      <c r="W28" s="34"/>
+      <c r="X28" s="33"/>
       <c r="Y28"/>
       <c r="Z28"/>
       <c r="AA28"/>
@@ -3216,44 +3353,50 @@
       <c r="BG28"/>
     </row>
     <row r="29" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="69"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="M29" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="N29" s="71"/>
-      <c r="O29" s="74"/>
-      <c r="P29" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q29" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="R29" s="74"/>
-      <c r="S29" s="73"/>
-      <c r="T29" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="U29" s="74"/>
-      <c r="V29" s="73"/>
-      <c r="W29" s="73"/>
-      <c r="X29" s="71"/>
+      <c r="A29" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="I29" s="31"/>
+      <c r="J29" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K29" s="31"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="P29" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q29" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="R29" s="35"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="U29" s="35"/>
+      <c r="V29" s="34"/>
+      <c r="W29" s="34"/>
+      <c r="X29" s="33"/>
       <c r="Y29"/>
       <c r="Z29"/>
       <c r="AA29"/>
@@ -3291,42 +3434,42 @@
       <c r="BG29"/>
     </row>
     <row r="30" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="69"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="J30" s="73"/>
-      <c r="K30" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="L30" s="74"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="71"/>
-      <c r="R30" s="74"/>
-      <c r="S30" s="73"/>
-      <c r="T30" s="71"/>
-      <c r="U30" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="V30" s="73"/>
-      <c r="W30" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="X30" s="71"/>
+      <c r="A30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="37"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" s="34"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K30" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="L30" s="35"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="33"/>
       <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
@@ -3364,30 +3507,44 @@
       <c r="BG30"/>
     </row>
     <row r="31" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="90"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="90"/>
-      <c r="F31" s="90"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="73"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="74"/>
-      <c r="S31" s="73"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="74"/>
-      <c r="V31" s="73"/>
-      <c r="W31" s="73"/>
-      <c r="X31" s="71"/>
+      <c r="A31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="31"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="32"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="J31" s="34"/>
+      <c r="K31" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="L31" s="35"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="U31" s="35"/>
+      <c r="V31" s="34"/>
+      <c r="W31" s="34"/>
+      <c r="X31" s="33"/>
       <c r="Y31"/>
       <c r="Z31"/>
       <c r="AA31"/>
@@ -3425,30 +3582,38 @@
       <c r="BG31"/>
     </row>
     <row r="32" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="90"/>
-      <c r="B32" s="90"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="74"/>
-      <c r="S32" s="73"/>
-      <c r="T32" s="71"/>
-      <c r="U32" s="74"/>
-      <c r="V32" s="73"/>
-      <c r="W32" s="73"/>
-      <c r="X32" s="71"/>
+      <c r="A32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="31"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="J32" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="K32" s="31"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="33"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="34"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="33"/>
       <c r="Y32"/>
       <c r="Z32"/>
       <c r="AA32"/>
@@ -3486,30 +3651,44 @@
       <c r="BG32"/>
     </row>
     <row r="33" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="90"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="90"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="73"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="73"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="74"/>
-      <c r="P33" s="73"/>
-      <c r="Q33" s="71"/>
-      <c r="R33" s="74"/>
-      <c r="S33" s="73"/>
-      <c r="T33" s="71"/>
-      <c r="U33" s="74"/>
-      <c r="V33" s="73"/>
-      <c r="W33" s="73"/>
-      <c r="X33" s="71"/>
+      <c r="A33" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="P33" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q33" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="R33" s="35"/>
+      <c r="S33" s="34"/>
+      <c r="T33" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="U33" s="35"/>
+      <c r="V33" s="34"/>
+      <c r="W33" s="34"/>
+      <c r="X33" s="33"/>
       <c r="Y33"/>
       <c r="Z33"/>
       <c r="AA33"/>
@@ -3547,30 +3726,30 @@
       <c r="BG33"/>
     </row>
     <row r="34" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="73"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="74"/>
-      <c r="M34" s="73"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="74"/>
-      <c r="P34" s="73"/>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="74"/>
-      <c r="S34" s="73"/>
-      <c r="T34" s="71"/>
-      <c r="U34" s="74"/>
-      <c r="V34" s="73"/>
-      <c r="W34" s="73"/>
-      <c r="X34" s="71"/>
+      <c r="A34" s="64"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="34"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="34"/>
+      <c r="W34" s="34"/>
+      <c r="X34" s="33"/>
       <c r="Y34"/>
       <c r="Z34"/>
       <c r="AA34"/>
@@ -3608,30 +3787,30 @@
       <c r="BG34"/>
     </row>
     <row r="35" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="19"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="74"/>
-      <c r="J35" s="73"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="74"/>
-      <c r="M35" s="73"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="74"/>
-      <c r="P35" s="73"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="74"/>
-      <c r="S35" s="73"/>
-      <c r="T35" s="71"/>
-      <c r="U35" s="74"/>
-      <c r="V35" s="73"/>
-      <c r="W35" s="73"/>
-      <c r="X35" s="71"/>
+      <c r="A35" s="64"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="34"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="34"/>
+      <c r="W35" s="34"/>
+      <c r="X35" s="33"/>
       <c r="Y35"/>
       <c r="Z35"/>
       <c r="AA35"/>
@@ -3669,30 +3848,30 @@
       <c r="BG35"/>
     </row>
     <row r="36" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="79"/>
-      <c r="J36" s="80"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="79"/>
-      <c r="M36" s="80"/>
-      <c r="N36" s="78"/>
-      <c r="O36" s="79"/>
-      <c r="P36" s="80"/>
-      <c r="Q36" s="78"/>
-      <c r="R36" s="79"/>
-      <c r="S36" s="80"/>
-      <c r="T36" s="78"/>
-      <c r="U36" s="79"/>
-      <c r="V36" s="80"/>
-      <c r="W36" s="80"/>
-      <c r="X36" s="71"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="34"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="35"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="34"/>
+      <c r="W36" s="34"/>
+      <c r="X36" s="33"/>
       <c r="Y36"/>
       <c r="Z36"/>
       <c r="AA36"/>
@@ -3730,30 +3909,30 @@
       <c r="BG36"/>
     </row>
     <row r="37" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="79"/>
-      <c r="J37" s="80"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="79"/>
-      <c r="M37" s="80"/>
-      <c r="N37" s="78"/>
-      <c r="O37" s="79"/>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="78"/>
-      <c r="R37" s="79"/>
-      <c r="S37" s="80"/>
-      <c r="T37" s="78"/>
-      <c r="U37" s="79"/>
-      <c r="V37" s="80"/>
-      <c r="W37" s="80"/>
-      <c r="X37" s="71"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="34"/>
+      <c r="T37" s="33"/>
+      <c r="U37" s="35"/>
+      <c r="V37" s="34"/>
+      <c r="W37" s="34"/>
+      <c r="X37" s="33"/>
       <c r="Y37"/>
       <c r="Z37"/>
       <c r="AA37"/>
@@ -3791,30 +3970,30 @@
       <c r="BG37"/>
     </row>
     <row r="38" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="80"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="79"/>
-      <c r="M38" s="80"/>
-      <c r="N38" s="78"/>
-      <c r="O38" s="79"/>
-      <c r="P38" s="80"/>
-      <c r="Q38" s="78"/>
-      <c r="R38" s="79"/>
-      <c r="S38" s="80"/>
-      <c r="T38" s="78"/>
-      <c r="U38" s="79"/>
-      <c r="V38" s="80"/>
-      <c r="W38" s="80"/>
-      <c r="X38" s="71"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="41"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="39"/>
+      <c r="R38" s="40"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="39"/>
+      <c r="U38" s="40"/>
+      <c r="V38" s="41"/>
+      <c r="W38" s="41"/>
+      <c r="X38" s="33"/>
       <c r="Y38"/>
       <c r="Z38"/>
       <c r="AA38"/>
@@ -3852,30 +4031,30 @@
       <c r="BG38"/>
     </row>
     <row r="39" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="78"/>
-      <c r="L39" s="79"/>
-      <c r="M39" s="80"/>
-      <c r="N39" s="78"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="78"/>
-      <c r="R39" s="79"/>
-      <c r="S39" s="80"/>
-      <c r="T39" s="78"/>
-      <c r="U39" s="79"/>
-      <c r="V39" s="80"/>
-      <c r="W39" s="80"/>
-      <c r="X39" s="71"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="41"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="41"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="39"/>
+      <c r="R39" s="40"/>
+      <c r="S39" s="41"/>
+      <c r="T39" s="39"/>
+      <c r="U39" s="40"/>
+      <c r="V39" s="41"/>
+      <c r="W39" s="41"/>
+      <c r="X39" s="33"/>
       <c r="Y39"/>
       <c r="Z39"/>
       <c r="AA39"/>
@@ -3913,30 +4092,30 @@
       <c r="BG39"/>
     </row>
     <row r="40" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="22"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="82"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="74"/>
-      <c r="J40" s="73"/>
-      <c r="K40" s="71"/>
-      <c r="L40" s="74"/>
-      <c r="M40" s="73"/>
-      <c r="N40" s="71"/>
-      <c r="O40" s="74"/>
-      <c r="P40" s="73"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="74"/>
-      <c r="S40" s="73"/>
-      <c r="T40" s="71"/>
-      <c r="U40" s="74"/>
-      <c r="V40" s="73"/>
-      <c r="W40" s="73"/>
-      <c r="X40" s="78"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="41"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="41"/>
+      <c r="N40" s="39"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="39"/>
+      <c r="R40" s="40"/>
+      <c r="S40" s="41"/>
+      <c r="T40" s="39"/>
+      <c r="U40" s="40"/>
+      <c r="V40" s="41"/>
+      <c r="W40" s="41"/>
+      <c r="X40" s="33"/>
       <c r="Y40"/>
       <c r="Z40"/>
       <c r="AA40"/>
@@ -3974,30 +4153,30 @@
       <c r="BG40"/>
     </row>
     <row r="41" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="74"/>
-      <c r="J41" s="73"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="74"/>
-      <c r="M41" s="73"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="74"/>
-      <c r="P41" s="73"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="74"/>
-      <c r="S41" s="73"/>
-      <c r="T41" s="71"/>
-      <c r="U41" s="74"/>
-      <c r="V41" s="73"/>
-      <c r="W41" s="73"/>
-      <c r="X41" s="78"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="41"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="39"/>
+      <c r="R41" s="40"/>
+      <c r="S41" s="41"/>
+      <c r="T41" s="39"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="41"/>
+      <c r="W41" s="41"/>
+      <c r="X41" s="33"/>
       <c r="Y41"/>
       <c r="Z41"/>
       <c r="AA41"/>
@@ -4034,31 +4213,31 @@
       <c r="BF41"/>
       <c r="BG41"/>
     </row>
-    <row r="42" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="21"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="86"/>
-      <c r="I42" s="87"/>
-      <c r="J42" s="88"/>
-      <c r="K42" s="86"/>
-      <c r="L42" s="87"/>
-      <c r="M42" s="88"/>
-      <c r="N42" s="86"/>
-      <c r="O42" s="87"/>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="86"/>
-      <c r="R42" s="87"/>
-      <c r="S42" s="88"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="87"/>
-      <c r="V42" s="88"/>
-      <c r="W42" s="88"/>
-      <c r="X42" s="89"/>
+    <row r="42" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="35"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="35"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="35"/>
+      <c r="S42" s="34"/>
+      <c r="T42" s="33"/>
+      <c r="U42" s="35"/>
+      <c r="V42" s="34"/>
+      <c r="W42" s="34"/>
+      <c r="X42" s="39"/>
       <c r="Y42"/>
       <c r="Z42"/>
       <c r="AA42"/>
@@ -4096,30 +4275,30 @@
       <c r="BG42"/>
     </row>
     <row r="43" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="33"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="35"/>
+      <c r="S43" s="34"/>
+      <c r="T43" s="33"/>
+      <c r="U43" s="35"/>
+      <c r="V43" s="34"/>
+      <c r="W43" s="34"/>
+      <c r="X43" s="39"/>
       <c r="Y43"/>
       <c r="Z43"/>
       <c r="AA43"/>
@@ -4157,30 +4336,30 @@
       <c r="BG43"/>
     </row>
     <row r="44" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44"/>
-      <c r="B44"/>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
-      <c r="I44"/>
-      <c r="J44"/>
-      <c r="K44"/>
-      <c r="L44"/>
-      <c r="M44"/>
-      <c r="N44"/>
-      <c r="O44"/>
-      <c r="P44"/>
-      <c r="Q44"/>
-      <c r="R44"/>
-      <c r="S44"/>
-      <c r="T44"/>
-      <c r="U44"/>
-      <c r="V44"/>
-      <c r="W44"/>
-      <c r="X44"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="48"/>
+      <c r="M44" s="49"/>
+      <c r="N44" s="47"/>
+      <c r="O44" s="48"/>
+      <c r="P44" s="49"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="48"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="47"/>
+      <c r="U44" s="48"/>
+      <c r="V44" s="49"/>
+      <c r="W44" s="49"/>
+      <c r="X44" s="50"/>
       <c r="Y44"/>
       <c r="Z44"/>
       <c r="AA44"/>
@@ -4217,31 +4396,31 @@
       <c r="BF44"/>
       <c r="BG44"/>
     </row>
-    <row r="45" spans="1:59" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-      <c r="B45"/>
-      <c r="C45"/>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
-      <c r="P45"/>
-      <c r="Q45"/>
-      <c r="R45"/>
-      <c r="S45"/>
-      <c r="T45"/>
-      <c r="U45"/>
-      <c r="V45"/>
-      <c r="W45"/>
-      <c r="X45"/>
+    <row r="45" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
       <c r="Y45"/>
       <c r="Z45"/>
       <c r="AA45"/>
@@ -4278,8 +4457,128 @@
       <c r="BF45"/>
       <c r="BG45"/>
     </row>
-    <row r="46" spans="1:59" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:59" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:59" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
+      <c r="AF46"/>
+      <c r="AG46"/>
+      <c r="AH46"/>
+      <c r="AI46"/>
+      <c r="AJ46"/>
+      <c r="AK46"/>
+      <c r="AL46"/>
+      <c r="AM46"/>
+      <c r="AN46"/>
+      <c r="AO46"/>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+      <c r="AR46"/>
+      <c r="AS46"/>
+      <c r="AT46"/>
+      <c r="AU46"/>
+      <c r="AV46"/>
+      <c r="AW46"/>
+      <c r="AX46"/>
+      <c r="AY46"/>
+      <c r="AZ46"/>
+      <c r="BA46"/>
+      <c r="BB46"/>
+      <c r="BC46"/>
+      <c r="BD46"/>
+      <c r="BE46"/>
+      <c r="BF46"/>
+      <c r="BG46"/>
+    </row>
+    <row r="47" spans="1:59" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47"/>
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+      <c r="Y47"/>
+      <c r="Z47"/>
+      <c r="AA47"/>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47"/>
+      <c r="AF47"/>
+      <c r="AG47"/>
+      <c r="AH47"/>
+      <c r="AI47"/>
+      <c r="AJ47"/>
+      <c r="AK47"/>
+      <c r="AL47"/>
+      <c r="AM47"/>
+      <c r="AN47"/>
+      <c r="AO47"/>
+      <c r="AP47"/>
+      <c r="AQ47"/>
+      <c r="AR47"/>
+      <c r="AS47"/>
+      <c r="AT47"/>
+      <c r="AU47"/>
+      <c r="AV47"/>
+      <c r="AW47"/>
+      <c r="AX47"/>
+      <c r="AY47"/>
+      <c r="AZ47"/>
+      <c r="BA47"/>
+      <c r="BB47"/>
+      <c r="BC47"/>
+      <c r="BD47"/>
+      <c r="BE47"/>
+      <c r="BF47"/>
+      <c r="BG47"/>
+    </row>
     <row r="48" spans="1:59" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -4322,73 +4621,75 @@
     <row r="87" spans="1:24" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="88" spans="1:24" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="1:24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
-      <c r="M90" s="1"/>
-      <c r="N90" s="1"/>
-      <c r="O90" s="1"/>
-      <c r="P90" s="1"/>
-      <c r="Q90" s="1"/>
-      <c r="R90" s="1"/>
-      <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
-      <c r="U90" s="1"/>
-      <c r="V90" s="1"/>
-      <c r="W90" s="1"/>
-      <c r="X90" s="1"/>
-    </row>
-    <row r="91" spans="1:24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-      <c r="M91" s="1"/>
-      <c r="N91" s="1"/>
-      <c r="O91" s="1"/>
-      <c r="P91" s="1"/>
-      <c r="Q91" s="1"/>
-      <c r="R91" s="1"/>
-      <c r="S91" s="1"/>
-      <c r="T91" s="1"/>
-      <c r="U91" s="1"/>
-      <c r="V91" s="1"/>
-      <c r="W91" s="1"/>
-      <c r="X91" s="1"/>
+    <row r="90" spans="1:24" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:24" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
+      <c r="T92" s="1"/>
+      <c r="U92" s="1"/>
+      <c r="V92" s="1"/>
+      <c r="W92" s="1"/>
+      <c r="X92" s="1"/>
+    </row>
+    <row r="93" spans="1:24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A26:X26"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A9:X9"/>
     <mergeCell ref="A24:X24"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="A8:X8"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="A5:X5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:T6"/>
-    <mergeCell ref="U6:X6"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="U7:X7"/>
     <mergeCell ref="G1:X1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
